--- a/AAII_Financials/Yearly/ICLR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ICLR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>ICLR</t>
   </si>
@@ -783,10 +783,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6069600</v>
+        <v>6076300</v>
       </c>
       <c r="E9" s="3">
-        <v>5810400</v>
+        <v>5817800</v>
       </c>
       <c r="F9" s="3">
         <v>5698400</v>
@@ -834,10 +834,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2181700</v>
+        <v>2175100</v>
       </c>
       <c r="E10" s="3">
-        <v>2378600</v>
+        <v>2371200</v>
       </c>
       <c r="F10" s="3">
         <v>2356500</v>
@@ -1007,11 +1007,11 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>569600</v>
-      </c>
-      <c r="E14" s="3">
-        <v>121700</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
         <v>89600</v>
@@ -1059,10 +1059,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>383000</v>
+        <v>280100</v>
       </c>
       <c r="E15" s="3">
-        <v>488500</v>
+        <v>398100</v>
       </c>
       <c r="F15" s="3">
         <v>586000</v>
@@ -1128,10 +1128,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7238900</v>
+        <v>7824300</v>
       </c>
       <c r="E17" s="3">
-        <v>7034900</v>
+        <v>7152400</v>
       </c>
       <c r="F17" s="3">
         <v>7060700</v>
@@ -1179,10 +1179,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1012500</v>
+        <v>427100</v>
       </c>
       <c r="E18" s="3">
-        <v>1154100</v>
+        <v>1036600</v>
       </c>
       <c r="F18" s="3">
         <v>994200</v>
@@ -1250,11 +1250,11 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>31000</v>
       </c>
       <c r="F20" s="3">
         <v>400</v>
@@ -1302,10 +1302,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1395500</v>
+        <v>697800</v>
       </c>
       <c r="E21" s="3">
-        <v>1642600</v>
+        <v>1403600</v>
       </c>
       <c r="F21" s="3">
         <v>1579800</v>
@@ -1353,10 +1353,10 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>197500</v>
+        <v>194300</v>
       </c>
       <c r="E22" s="3">
-        <v>237200</v>
+        <v>211600</v>
       </c>
       <c r="F22" s="3">
         <v>336700</v>
@@ -1404,10 +1404,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>252500</v>
+        <v>230500</v>
       </c>
       <c r="E23" s="3">
-        <v>803800</v>
+        <v>802600</v>
       </c>
       <c r="F23" s="3">
         <v>572600</v>
@@ -1455,10 +1455,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>23100</v>
+        <v>16500</v>
       </c>
       <c r="E24" s="3">
-        <v>64600</v>
+        <v>75500</v>
       </c>
       <c r="F24" s="3">
         <v>18400</v>
@@ -1557,10 +1557,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>229300</v>
+        <v>214000</v>
       </c>
       <c r="E26" s="3">
-        <v>739100</v>
+        <v>727100</v>
       </c>
       <c r="F26" s="3">
         <v>554200</v>
@@ -1608,10 +1608,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>229300</v>
+        <v>214000</v>
       </c>
       <c r="E27" s="3">
-        <v>739100</v>
+        <v>727100</v>
       </c>
       <c r="F27" s="3">
         <v>554200</v>
@@ -1862,11 +1862,11 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-31000</v>
       </c>
       <c r="F32" s="3">
         <v>-400</v>
@@ -1914,10 +1914,10 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>229300</v>
+        <v>214000</v>
       </c>
       <c r="E33" s="3">
-        <v>739100</v>
+        <v>727100</v>
       </c>
       <c r="F33" s="3">
         <v>554200</v>
@@ -2016,10 +2016,10 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>229300</v>
+        <v>214000</v>
       </c>
       <c r="E35" s="3">
-        <v>739100</v>
+        <v>727100</v>
       </c>
       <c r="F35" s="3">
         <v>554200</v>
@@ -2267,10 +2267,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2749100</v>
+        <v>2744400</v>
       </c>
       <c r="E43" s="3">
-        <v>2595900</v>
+        <v>2613500</v>
       </c>
       <c r="F43" s="3">
         <v>2775000</v>
@@ -2317,11 +2317,11 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>8</v>
+      <c r="D44" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>8400</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>8</v>
@@ -2522,10 +2522,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>524700</v>
+        <v>319600</v>
       </c>
       <c r="E48" s="3">
-        <v>530500</v>
+        <v>312400</v>
       </c>
       <c r="F48" s="3">
         <v>501500</v>
@@ -2573,10 +2573,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>11978800</v>
+        <v>12227500</v>
       </c>
       <c r="E49" s="3">
-        <v>12611200</v>
+        <v>12877800</v>
       </c>
       <c r="F49" s="3">
         <v>12877900</v>
@@ -2726,10 +2726,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>75700</v>
+        <v>51600</v>
       </c>
       <c r="E52" s="3">
-        <v>84200</v>
+        <v>59400</v>
       </c>
       <c r="F52" s="3">
         <v>78500</v>
@@ -2828,10 +2828,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16269800</v>
+        <v>16332900</v>
       </c>
       <c r="E54" s="3">
-        <v>16634800</v>
+        <v>16693400</v>
       </c>
       <c r="F54" s="3">
         <v>16864800</v>
@@ -2921,10 +2921,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>353800</v>
+        <v>780900</v>
       </c>
       <c r="E57" s="3">
-        <v>328800</v>
+        <v>698000</v>
       </c>
       <c r="F57" s="3">
         <v>262500</v>
@@ -3023,10 +3023,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1609100</v>
+        <v>1724300</v>
       </c>
       <c r="E59" s="3">
-        <v>1652400</v>
+        <v>1779900</v>
       </c>
       <c r="F59" s="3">
         <v>1610000</v>
@@ -3074,10 +3074,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3196200</v>
+        <v>3311400</v>
       </c>
       <c r="E60" s="3">
-        <v>2635500</v>
+        <v>2763000</v>
       </c>
       <c r="F60" s="3">
         <v>2730300</v>
@@ -3176,10 +3176,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>176100</v>
+        <v>56900</v>
       </c>
       <c r="E62" s="3">
-        <v>210300</v>
+        <v>66100</v>
       </c>
       <c r="F62" s="3">
         <v>233000</v>
@@ -3380,10 +3380,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7076400</v>
+        <v>7086000</v>
       </c>
       <c r="E66" s="3">
-        <v>7193500</v>
+        <v>7192400</v>
       </c>
       <c r="F66" s="3">
         <v>7653300</v>
@@ -3656,10 +3656,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2122100</v>
+        <v>2691800</v>
       </c>
       <c r="E72" s="3">
-        <v>2643200</v>
+        <v>3162600</v>
       </c>
       <c r="F72" s="3">
         <v>2404400</v>
@@ -3860,10 +3860,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9193400</v>
+        <v>9246900</v>
       </c>
       <c r="E76" s="3">
-        <v>9441400</v>
+        <v>9501000</v>
       </c>
       <c r="F76" s="3">
         <v>9211400</v>
@@ -4018,10 +4018,10 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>229300</v>
+        <v>214000</v>
       </c>
       <c r="E81" s="3">
-        <v>739100</v>
+        <v>727100</v>
       </c>
       <c r="F81" s="3">
         <v>554200</v>
@@ -4090,10 +4090,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>155800</v>
+        <v>90500</v>
       </c>
       <c r="E83" s="3">
-        <v>138200</v>
+        <v>88800</v>
       </c>
       <c r="F83" s="3">
         <v>126100</v>
@@ -4396,10 +4396,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1036200</v>
+        <v>1078200</v>
       </c>
       <c r="E89" s="3">
-        <v>1286700</v>
+        <v>1334400</v>
       </c>
       <c r="F89" s="3">
         <v>1161000</v>
@@ -4468,10 +4468,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-174200</v>
+        <v>-69800</v>
       </c>
       <c r="E91" s="3">
-        <v>-168100</v>
+        <v>-56800</v>
       </c>
       <c r="F91" s="3">
         <v>-140700</v>
@@ -4897,10 +4897,10 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-771300</v>
+        <v>-813200</v>
       </c>
       <c r="E100" s="3">
-        <v>-837200</v>
+        <v>-884900</v>
       </c>
       <c r="F100" s="3">
         <v>-844000</v>
